--- a/BeatnotePostHotCell/May28,2026/Fit_ResultMay28.xlsx
+++ b/BeatnotePostHotCell/May28,2026/Fit_ResultMay28.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\BeatnotePostHotCell\May28,2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AB272AB-B06A-47AE-BB4B-415AC56B9DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF9AE08-634A-4F8A-A13C-3B1037E19C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{D9E101C5-8284-4B59-8B1C-2AD2D5F2FDD3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="28">
   <si>
     <t>Date</t>
   </si>
@@ -65,12 +65,6 @@
     <t>May28,2026+1-37-31PM</t>
   </si>
   <si>
-    <t>May28,2026+11-51-56AM</t>
-  </si>
-  <si>
-    <t>May28,2026+12-26-46PM</t>
-  </si>
-  <si>
     <t>May28,2026+2-22-26PM</t>
   </si>
   <si>
@@ -101,49 +95,34 @@
     <t>May28,2026+3-37-09PM</t>
   </si>
   <si>
-    <t>May28,2026+3-49-20PM</t>
-  </si>
-  <si>
     <t>May28,2026+3-59-05PM</t>
   </si>
   <si>
-    <t>May28,2026+4-08-39PM</t>
-  </si>
-  <si>
     <t>May28,2026+4-16-31PM</t>
   </si>
   <si>
     <t>May28,2026+4-36-20PM</t>
   </si>
   <si>
-    <t>May28,2026+4-48-24PM</t>
-  </si>
-  <si>
-    <t>May28,2026+4-58-22PM</t>
-  </si>
-  <si>
     <t>May28,2026+5-15-31PM</t>
   </si>
   <si>
     <t>May28,2026+5-23-41PM</t>
   </si>
   <si>
-    <t>May28,2026+5-31-48PM</t>
-  </si>
-  <si>
     <t>May28,2026+5-39-46PM</t>
   </si>
   <si>
     <t>May28,2026+6-01-12PM</t>
   </si>
   <si>
-    <t>h2</t>
-  </si>
-  <si>
     <t>mean</t>
   </si>
   <si>
     <t>std</t>
+  </si>
+  <si>
+    <t>offset</t>
   </si>
 </sst>
 </file>
@@ -538,16 +517,16 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="42.75">
@@ -555,25 +534,25 @@
         <v>7</v>
       </c>
       <c r="B2" s="1">
-        <v>0.39075425090921301</v>
+        <v>0.30390235043574698</v>
       </c>
       <c r="C2" s="1">
-        <v>1.4905490974729301</v>
+        <v>1.48487750627935</v>
       </c>
       <c r="D2" s="1">
-        <v>-11.056497237999899</v>
+        <v>-1.0259315949263401E-3</v>
       </c>
       <c r="E2" s="2">
-        <v>-4.6394866255121999E-5</v>
+        <v>-4.6394521161871E-5</v>
       </c>
       <c r="F2" s="1">
-        <v>3.5613195963412498</v>
+        <v>3.5001767880955099</v>
       </c>
       <c r="G2" s="1">
-        <v>63.443282631024303</v>
+        <v>62.447894969605301</v>
       </c>
       <c r="H2" s="1">
-        <v>1.15112995116531E-3</v>
+        <v>7.5215458405789005E-4</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75">
@@ -581,25 +560,25 @@
         <v>8</v>
       </c>
       <c r="B3" s="1">
-        <v>0.382603274453377</v>
+        <v>0.30438419283964002</v>
       </c>
       <c r="C3" s="1">
-        <v>1.48748116910918</v>
+        <v>1.4837879279099899</v>
       </c>
       <c r="D3" s="1">
-        <v>-2.0257808480688899E-3</v>
+        <v>-1.57487840653377E-3</v>
       </c>
       <c r="E3" s="2">
-        <v>7.0209059026860593E-5</v>
+        <v>4.0376541549654297E-5</v>
       </c>
       <c r="F3" s="1">
-        <v>3.6462509395362899</v>
+        <v>2.00575085139804</v>
       </c>
       <c r="G3" s="1">
-        <v>63.3286749801144</v>
+        <v>63.441678149655097</v>
       </c>
       <c r="H3" s="1">
-        <v>1.15536261605784E-3</v>
+        <v>1.15715386863374E-3</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="42.75">
@@ -607,25 +586,25 @@
         <v>9</v>
       </c>
       <c r="B4" s="1">
-        <v>0.39308947006408002</v>
+        <v>0.297161130585052</v>
       </c>
       <c r="C4" s="1">
-        <v>1.4838977883584801</v>
+        <v>1.4832129968194401</v>
       </c>
       <c r="D4" s="1">
-        <v>-7.1624067823997204E-4</v>
-      </c>
-      <c r="E4" s="2">
-        <v>-9.0836229937458202E-5</v>
+        <v>-2.22918801331387E-3</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1.5548819591606699E-4</v>
       </c>
       <c r="F4" s="1">
-        <v>3.6401556043666701</v>
+        <v>2.00141941245752</v>
       </c>
       <c r="G4" s="1">
-        <v>63.4675558545296</v>
+        <v>61.439773238678399</v>
       </c>
       <c r="H4" s="1">
-        <v>1.13505299747706E-3</v>
+        <v>5.7857733312214102E-4</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="42.75">
@@ -633,25 +612,25 @@
         <v>10</v>
       </c>
       <c r="B5" s="1">
-        <v>0.39090251610402299</v>
+        <v>0.30092447877826201</v>
       </c>
       <c r="C5" s="1">
-        <v>1.4837879279099899</v>
+        <v>1.4845336497847099</v>
       </c>
       <c r="D5" s="1">
-        <v>-1.57487840653377E-3</v>
+        <v>-1.09572408510595E-3</v>
       </c>
       <c r="E5" s="2">
-        <v>4.0376541549654297E-5</v>
+        <v>-5.89400129811551E-5</v>
       </c>
       <c r="F5" s="1">
-        <v>2.0668804140352699</v>
+        <v>2.99810563914619</v>
       </c>
       <c r="G5" s="1">
-        <v>63.441366201157699</v>
+        <v>61.458936733142899</v>
       </c>
       <c r="H5" s="1">
-        <v>1.1470989971767401E-3</v>
+        <v>5.8142863020411496E-4</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="42.75">
@@ -659,25 +638,25 @@
         <v>11</v>
       </c>
       <c r="B6" s="1">
-        <v>0.38163793874347302</v>
+        <v>0.30225556251139701</v>
       </c>
       <c r="C6" s="1">
-        <v>1.4832129968194401</v>
+        <v>1.4845506138856599</v>
       </c>
       <c r="D6" s="1">
-        <v>-2.22918801331387E-3</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1.5548819591606699E-4</v>
+        <v>-1.13127563346766E-3</v>
+      </c>
+      <c r="E6" s="2">
+        <v>-5.39990017829683E-5</v>
       </c>
       <c r="F6" s="1">
-        <v>2.0625628723508198</v>
+        <v>2.7467118677007698</v>
       </c>
       <c r="G6" s="1">
-        <v>61.439773030001497</v>
+        <v>61.447470152952903</v>
       </c>
       <c r="H6" s="1">
-        <v>5.7857693707981698E-4</v>
+        <v>5.7919060686151096E-4</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="42.75">
@@ -685,25 +664,25 @@
         <v>12</v>
       </c>
       <c r="B7" s="1">
-        <v>0.38646897393750201</v>
+        <v>0.30453505035585898</v>
       </c>
       <c r="C7" s="1">
-        <v>1.4845336497847099</v>
+        <v>1.4854392248277599</v>
       </c>
       <c r="D7" s="1">
-        <v>-1.09572408510595E-3</v>
+        <v>-1.3989463873914599E-3</v>
       </c>
       <c r="E7" s="2">
-        <v>-5.89400129811551E-5</v>
+        <v>6.1726508546467696E-7</v>
       </c>
       <c r="F7" s="1">
-        <v>3.0592330668630501</v>
+        <v>3.2542985883723099</v>
       </c>
       <c r="G7" s="1">
-        <v>61.458935990008897</v>
+        <v>63.438473334628</v>
       </c>
       <c r="H7" s="1">
-        <v>5.7857693655743601E-4</v>
+        <v>1.15609543834572E-3</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="42.75">
@@ -711,25 +690,25 @@
         <v>13</v>
       </c>
       <c r="B8" s="1">
-        <v>0.38820632020412599</v>
+        <v>0.29441937543381203</v>
       </c>
       <c r="C8" s="1">
-        <v>1.4845506138856599</v>
+        <v>1.48420988493761</v>
       </c>
       <c r="D8" s="1">
-        <v>-1.13127563346766E-3</v>
+        <v>-9.8591795740126591E-4</v>
       </c>
       <c r="E8" s="2">
-        <v>-5.39990017829683E-5</v>
+        <v>-6.8577069492968703E-5</v>
       </c>
       <c r="F8" s="1">
-        <v>2.8078625870111198</v>
+        <v>3.0024737934188601</v>
       </c>
       <c r="G8" s="1">
-        <v>61.410458831613397</v>
+        <v>61.424360450047203</v>
       </c>
       <c r="H8" s="1">
-        <v>6.43399693013518E-4</v>
+        <v>5.7857693432255305E-4</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="42.75">
@@ -737,25 +716,25 @@
         <v>14</v>
       </c>
       <c r="B9" s="1">
-        <v>0.391100077546855</v>
+        <v>0.29938049893952201</v>
       </c>
       <c r="C9" s="1">
-        <v>1.4854392248277599</v>
+        <v>1.4846546239851801</v>
       </c>
       <c r="D9" s="1">
-        <v>-1.3989463873914599E-3</v>
+        <v>-1.4726402124876699E-3</v>
       </c>
       <c r="E9" s="2">
-        <v>6.1726508546467696E-7</v>
+        <v>1.2774295622833399E-5</v>
       </c>
       <c r="F9" s="1">
-        <v>3.3154314210110098</v>
+        <v>2.5051482864221599</v>
       </c>
       <c r="G9" s="1">
-        <v>63.433519581560802</v>
+        <v>61.4303056702772</v>
       </c>
       <c r="H9" s="1">
-        <v>1.1512890755253E-3</v>
+        <v>5.7857693456894797E-4</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="42.75">
@@ -763,25 +742,25 @@
         <v>15</v>
       </c>
       <c r="B10" s="1">
-        <v>0.37812534333091802</v>
+        <v>0.30198767465833298</v>
       </c>
       <c r="C10" s="1">
-        <v>1.48420988493761</v>
+        <v>1.4843090766025</v>
       </c>
       <c r="D10" s="1">
-        <v>-9.8591795740126591E-4</v>
+        <v>-1.5625333950009201E-3</v>
       </c>
       <c r="E10" s="2">
-        <v>-6.8577069492968703E-5</v>
+        <v>2.53366754048281E-5</v>
       </c>
       <c r="F10" s="1">
-        <v>3.06362215736746</v>
+        <v>2.5021681326783898</v>
       </c>
       <c r="G10" s="1">
-        <v>61.424360450010603</v>
+        <v>61.407522204261603</v>
       </c>
       <c r="H10" s="1">
-        <v>5.7857693431707696E-4</v>
+        <v>6.3574155348453002E-4</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="42.75">
@@ -789,25 +768,25 @@
         <v>16</v>
       </c>
       <c r="B11" s="1">
-        <v>0.38449528426413199</v>
+        <v>0.29452133244947898</v>
       </c>
       <c r="C11" s="1">
-        <v>1.4846546239851801</v>
+        <v>1.4836975393277401</v>
       </c>
       <c r="D11" s="1">
-        <v>-1.4726402124876699E-3</v>
-      </c>
-      <c r="E11" s="2">
-        <v>1.2774295622833399E-5</v>
+        <v>-2.1447906871209601E-3</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1.42899271591477E-4</v>
       </c>
       <c r="F11" s="1">
-        <v>2.5662855762536898</v>
+        <v>1.7488369668618899</v>
       </c>
       <c r="G11" s="1">
-        <v>61.430305670004302</v>
+        <v>61.425917223720099</v>
       </c>
       <c r="H11" s="1">
-        <v>5.7857693431745795E-4</v>
+        <v>5.78576934825183E-4</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="42.75">
@@ -815,25 +794,25 @@
         <v>17</v>
       </c>
       <c r="B12" s="1">
-        <v>0.38779470041263903</v>
+        <v>0.30226636207287</v>
       </c>
       <c r="C12" s="1">
-        <v>1.4843090766025</v>
+        <v>1.48309107983707</v>
       </c>
       <c r="D12" s="1">
-        <v>-1.5625333950009201E-3</v>
+        <v>-1.2981348973399099E-3</v>
       </c>
       <c r="E12" s="2">
-        <v>2.53366754048281E-5</v>
+        <v>-7.3336441564362796E-5</v>
       </c>
       <c r="F12" s="1">
-        <v>2.5633325966549299</v>
+        <v>1.21927768138959</v>
       </c>
       <c r="G12" s="1">
-        <v>61.405457670584397</v>
+        <v>63.246976221369103</v>
       </c>
       <c r="H12" s="1">
-        <v>5.7906808430909797E-4</v>
+        <v>9.9703814398932893E-4</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="42.75">
@@ -841,25 +820,25 @@
         <v>18</v>
       </c>
       <c r="B13" s="1">
-        <v>0.37824803542534602</v>
+        <v>0.30276185184620003</v>
       </c>
       <c r="C13" s="1">
-        <v>1.4836975393277401</v>
+        <v>1.4836724052264101</v>
       </c>
       <c r="D13" s="1">
-        <v>-2.1447906871209601E-3</v>
-      </c>
-      <c r="E13" s="1">
-        <v>1.42899271591477E-4</v>
+        <v>-8.5906880509088995E-4</v>
+      </c>
+      <c r="E13" s="2">
+        <v>-8.91358415987863E-5</v>
       </c>
       <c r="F13" s="1">
-        <v>1.8100047855000401</v>
+        <v>3.00577248958141</v>
       </c>
       <c r="G13" s="1">
-        <v>61.425917220018199</v>
+        <v>63.421595139974698</v>
       </c>
       <c r="H13" s="1">
-        <v>5.7857693460873895E-4</v>
+        <v>1.15715386863381E-3</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="42.75">
@@ -867,25 +846,25 @@
         <v>19</v>
       </c>
       <c r="B14" s="1">
-        <v>0.388322173460803</v>
+        <v>0.30565983998385898</v>
       </c>
       <c r="C14" s="1">
-        <v>1.48309107983707</v>
+        <v>1.4826680808711501</v>
       </c>
       <c r="D14" s="1">
-        <v>-1.2981348973399099E-3</v>
+        <v>-1.42373444154237E-3</v>
       </c>
       <c r="E14" s="2">
-        <v>-7.3336441564362796E-5</v>
+        <v>6.1447219360036699E-6</v>
       </c>
       <c r="F14" s="1">
-        <v>1.2804286874771</v>
+        <v>2.2537703326013299</v>
       </c>
       <c r="G14" s="1">
-        <v>63.428015169997899</v>
+        <v>63.432151389991503</v>
       </c>
       <c r="H14" s="1">
-        <v>1.1571538686084E-3</v>
+        <v>1.15715386862106E-3</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="42.75">
@@ -893,25 +872,25 @@
         <v>20</v>
       </c>
       <c r="B15" s="1">
-        <v>0.39882150256402099</v>
+        <v>0.30235700258888798</v>
       </c>
       <c r="C15" s="1">
-        <v>1.4831024185505199</v>
+        <v>1.4854613385962101</v>
       </c>
       <c r="D15" s="1">
-        <v>-1.4903719055390399E-3</v>
+        <v>-1.5149028501038901E-3</v>
       </c>
       <c r="E15" s="2">
-        <v>1.76172535139362E-5</v>
+        <v>3.8792642770549997E-6</v>
       </c>
       <c r="F15" s="1">
-        <v>2.3186059019949301</v>
+        <v>2.5017366084783901</v>
       </c>
       <c r="G15" s="1">
-        <v>63.420744939986797</v>
+        <v>62.178086016031202</v>
       </c>
       <c r="H15" s="1">
-        <v>1.1571538686196399E-3</v>
+        <v>1.11966907210078E-3</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="42.75">
@@ -919,25 +898,25 @@
         <v>21</v>
       </c>
       <c r="B16" s="1">
-        <v>0.38881861759339797</v>
+        <v>0.30470031507930101</v>
       </c>
       <c r="C16" s="1">
-        <v>1.4836724052264101</v>
+        <v>1.4863049084100199</v>
       </c>
       <c r="D16" s="1">
-        <v>-8.5906880509088995E-4</v>
+        <v>-1.6884793599640101E-3</v>
       </c>
       <c r="E16" s="2">
-        <v>-8.91358415987863E-5</v>
+        <v>4.9440287294651503E-5</v>
       </c>
       <c r="F16" s="1">
-        <v>3.0669169038061801</v>
+        <v>2.4975932300343602</v>
       </c>
       <c r="G16" s="1">
-        <v>63.421595138818503</v>
+        <v>61.464651999573398</v>
       </c>
       <c r="H16" s="1">
-        <v>1.15715386790713E-3</v>
+        <v>5.7857693579339104E-4</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="42.75">
@@ -945,25 +924,25 @@
         <v>22</v>
       </c>
       <c r="B17" s="1">
-        <v>0.38168078365716102</v>
+        <v>0.30681032275950298</v>
       </c>
       <c r="C17" s="1">
-        <v>1.48245243868853</v>
+        <v>1.48570881320865</v>
       </c>
       <c r="D17" s="1">
-        <v>-1.9738324303088801E-3</v>
-      </c>
-      <c r="E17" s="1">
-        <v>1.48118663739377E-4</v>
+        <v>-1.1717898053942E-3</v>
+      </c>
+      <c r="E17" s="2">
+        <v>-3.0965558330159103E-5</v>
       </c>
       <c r="F17" s="1">
-        <v>1.82468938895384</v>
+        <v>2.9591559923467998</v>
       </c>
       <c r="G17" s="1">
-        <v>61.416826736685799</v>
+        <v>63.451136949977403</v>
       </c>
       <c r="H17" s="1">
-        <v>6.3558720640955802E-4</v>
+        <v>1.1571538686330899E-3</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="42.75">
@@ -971,25 +950,25 @@
         <v>23</v>
       </c>
       <c r="B18" s="1">
-        <v>0.39254780032303299</v>
+        <v>0.31003085423784599</v>
       </c>
       <c r="C18" s="1">
-        <v>1.4826680808711501</v>
+        <v>1.48710641337002</v>
       </c>
       <c r="D18" s="1">
-        <v>-1.42373444154237E-3</v>
+        <v>-1.6634857344520501E-3</v>
       </c>
       <c r="E18" s="2">
-        <v>6.1447219360036699E-6</v>
+        <v>4.85413898081714E-5</v>
       </c>
       <c r="F18" s="1">
-        <v>2.3148852261039101</v>
+        <v>2.5098234666122301</v>
       </c>
       <c r="G18" s="1">
-        <v>63.4321513851337</v>
+        <v>63.437356499918003</v>
       </c>
       <c r="H18" s="1">
-        <v>1.15715386606004E-3</v>
+        <v>1.1571538685425701E-3</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="42.75">
@@ -997,208 +976,96 @@
         <v>24</v>
       </c>
       <c r="B19" s="1">
-        <v>0.38860291038577099</v>
+        <v>0.30130891367381502</v>
       </c>
       <c r="C19" s="1">
-        <v>1.4854613385962101</v>
+        <v>1.4862231336915399</v>
       </c>
       <c r="D19" s="1">
-        <v>-1.5149028501038901E-3</v>
-      </c>
-      <c r="E19" s="2">
-        <v>3.8792642770549997E-6</v>
+        <v>-7.2219562726808201E-4</v>
+      </c>
+      <c r="E19" s="1">
+        <v>-1.2722889104584701E-4</v>
       </c>
       <c r="F19" s="1">
-        <v>2.5628866588624399</v>
+        <v>2.7571262265682899</v>
       </c>
       <c r="G19" s="1">
-        <v>63.442300896795302</v>
+        <v>61.484922658995899</v>
       </c>
       <c r="H19" s="1">
-        <v>1.1571390461673999E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="42.75">
-      <c r="A20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="1">
-        <v>0.381832928937616</v>
-      </c>
-      <c r="C20" s="1">
-        <v>1.4847631686204199</v>
-      </c>
-      <c r="D20" s="1">
-        <v>-1.7771097451962899E-3</v>
-      </c>
-      <c r="E20" s="2">
-        <v>4.3267764457533399E-5</v>
-      </c>
-      <c r="F20" s="1">
-        <v>2.5615262519667601</v>
-      </c>
-      <c r="G20" s="1">
-        <v>61.452271060046201</v>
-      </c>
-      <c r="H20" s="1">
-        <v>5.7857693431695304E-4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="42.75">
-      <c r="A21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="1">
-        <v>0.37399925074352303</v>
-      </c>
-      <c r="C21" s="1">
-        <v>1.4853469242862301</v>
-      </c>
-      <c r="D21" s="1">
-        <v>-1.4934144697666099E-3</v>
-      </c>
-      <c r="E21" s="2">
-        <v>3.1346279932709501E-5</v>
-      </c>
-      <c r="F21" s="1">
-        <v>2.8158161600481</v>
-      </c>
-      <c r="G21" s="1">
-        <v>61.465988640001697</v>
-      </c>
-      <c r="H21" s="1">
-        <v>5.7857693431711003E-4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="42.75">
-      <c r="A22" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="1">
-        <v>0.391344107724999</v>
-      </c>
-      <c r="C22" s="1">
-        <v>1.4863049084100199</v>
-      </c>
-      <c r="D22" s="1">
-        <v>-1.6884793599640101E-3</v>
-      </c>
-      <c r="E22" s="2">
-        <v>4.9440287294651503E-5</v>
-      </c>
-      <c r="F22" s="1">
-        <v>2.5587097522209001</v>
-      </c>
-      <c r="G22" s="1">
-        <v>61.474231986833303</v>
-      </c>
-      <c r="H22" s="1">
-        <v>6.1078119799516997E-4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="42.75">
-      <c r="A23" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="1">
-        <v>0.39401793952400199</v>
-      </c>
-      <c r="C23" s="1">
-        <v>1.48570881320865</v>
-      </c>
-      <c r="D23" s="1">
-        <v>-1.1717898053942E-3</v>
-      </c>
-      <c r="E23" s="2">
-        <v>-3.0965558330159103E-5</v>
-      </c>
-      <c r="F23" s="1">
-        <v>3.0202621738343698</v>
-      </c>
-      <c r="G23" s="1">
-        <v>63.4511369499997</v>
-      </c>
-      <c r="H23" s="1">
-        <v>1.1571538686334501E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="42.75">
-      <c r="A24" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" s="1">
-        <v>0.37236684560932298</v>
-      </c>
-      <c r="C24" s="1">
-        <v>1.48443598832473</v>
-      </c>
-      <c r="D24" s="1">
-        <v>6.0032452914508903E-4</v>
-      </c>
-      <c r="E24" s="1">
-        <v>-3.1227422912767302E-4</v>
-      </c>
-      <c r="F24" s="1">
-        <v>2.5622896089593699</v>
-      </c>
-      <c r="G24" s="1">
-        <v>61.435149929999902</v>
-      </c>
-      <c r="H24" s="1">
-        <v>5.7857693446708197E-4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="42.75">
-      <c r="A25" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="1">
-        <v>0.398157579716993</v>
-      </c>
-      <c r="C25" s="1">
-        <v>1.48710641337002</v>
-      </c>
-      <c r="D25" s="1">
-        <v>-1.6634857344520501E-3</v>
-      </c>
-      <c r="E25" s="2">
-        <v>4.85413898081714E-5</v>
-      </c>
-      <c r="F25" s="1">
-        <v>2.5709266468787701</v>
-      </c>
-      <c r="G25" s="1">
-        <v>63.437356499841101</v>
-      </c>
-      <c r="H25" s="1">
-        <v>1.15715386861533E-3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="42.75">
-      <c r="A26" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26" s="1">
-        <v>0.38710256673105198</v>
-      </c>
-      <c r="C26" s="1">
-        <v>1.4862231336915399</v>
-      </c>
-      <c r="D26" s="1">
-        <v>-7.2219562726808201E-4</v>
-      </c>
-      <c r="E26" s="1">
-        <v>-1.2722889104584701E-4</v>
-      </c>
-      <c r="F26" s="1">
-        <v>2.81828164832238</v>
-      </c>
-      <c r="G26" s="1">
-        <v>61.484823260261599</v>
-      </c>
-      <c r="H26" s="1">
-        <v>8.5188758254897397E-4</v>
-      </c>
+        <v>6.1429954356389497E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1260,7 +1127,7 @@
     </row>
     <row r="3" spans="1:8" ht="42.75">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1">
         <v>18.346083770183299</v>
@@ -1284,7 +1151,7 @@
     </row>
     <row r="4" spans="1:8" ht="42.75">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1">
         <v>18.452491695077299</v>
@@ -1308,7 +1175,7 @@
     </row>
     <row r="5" spans="1:8" ht="42.75">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1">
         <v>18.351915434355199</v>
@@ -1332,7 +1199,7 @@
     </row>
     <row r="6" spans="1:8" ht="42.75">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1">
         <v>18.337397032620899</v>
@@ -1356,7 +1223,7 @@
     </row>
     <row r="7" spans="1:8" ht="42.75">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1">
         <v>18.232394257417202</v>
@@ -1380,7 +1247,7 @@
     </row>
     <row r="8" spans="1:8" ht="42.75">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B8" s="1">
         <v>18.415074041865601</v>
@@ -1404,7 +1271,7 @@
     </row>
     <row r="9" spans="1:8" ht="42.75">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B9" s="1">
         <v>18.341941017083698</v>
@@ -1428,7 +1295,7 @@
     </row>
     <row r="10" spans="1:8" ht="42.75">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B10" s="1">
         <v>18.237027996635099</v>
@@ -1452,7 +1319,7 @@
     </row>
     <row r="11" spans="1:8" ht="42.75">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B11" s="1">
         <v>18.531243546545401</v>
@@ -1476,7 +1343,7 @@
     </row>
     <row r="12" spans="1:8" ht="42.75">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B12" s="1">
         <v>18.412716855394802</v>
@@ -1500,7 +1367,7 @@
     </row>
     <row r="13" spans="1:8" ht="42.75">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B13" s="1">
         <v>18.4923898758226</v>
@@ -1524,7 +1391,7 @@
     </row>
     <row r="14" spans="1:8" ht="42.75">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B14" s="1">
         <v>18.515382021503999</v>
@@ -1548,7 +1415,7 @@
     </row>
     <row r="15" spans="1:8" ht="42.75">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B15" s="1">
         <v>18.391192672959299</v>
@@ -1572,7 +1439,7 @@
     </row>
     <row r="16" spans="1:8" ht="42.75">
       <c r="A16" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B16" s="1">
         <v>18.551612310419799</v>
@@ -1596,7 +1463,7 @@
     </row>
     <row r="17" spans="1:8" ht="42.75">
       <c r="A17" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B17" s="1">
         <v>18.393990200449998</v>
@@ -1620,7 +1487,7 @@
     </row>
     <row r="18" spans="1:8" ht="42.75">
       <c r="A18" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B18" s="1">
         <v>18.450034969079201</v>
@@ -1644,7 +1511,7 @@
     </row>
     <row r="19" spans="1:8" ht="42.75">
       <c r="A19" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B19" s="1">
         <v>18.408277105199002</v>
@@ -1673,10 +1540,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF8CB368-1F4F-4C65-B86B-93EC676CB77B}">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1684,299 +1551,260 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="1" t="s">
         <v>1</v>
+      </c>
+      <c r="G1">
+        <v>894</v>
       </c>
       <c r="H1">
         <v>456</v>
       </c>
-      <c r="I1">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="42.75">
+    </row>
+    <row r="2" spans="1:11" ht="42.75">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="1">
-        <v>0.39075425090921301</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="1">
         <v>18.481531830496198</v>
       </c>
-      <c r="G2" t="s">
-        <v>33</v>
+      <c r="C2" s="1">
+        <v>0.30390235043574698</v>
+      </c>
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2">
+        <f>AVERAGE(B2:B19)</f>
+        <v>18.407927590728249</v>
       </c>
       <c r="H2">
-        <f>AVERAGE(B2:B19)</f>
-        <v>0.38814706418609157</v>
-      </c>
-      <c r="I2">
-        <f>AVERAGE(D2:D19)</f>
-        <v>18.407927590728249</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="42.75">
+        <f>AVERAGE(C2:C19)</f>
+        <v>0.30218706162385472</v>
+      </c>
+      <c r="J2" s="1"/>
+    </row>
+    <row r="3" spans="1:11" ht="42.75">
       <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1">
+        <v>18.346083770183299</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.30438419283964002</v>
+      </c>
+      <c r="F3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3">
+        <f>_xlfn.STDEV.S(B2:B19)</f>
+        <v>9.0932068938100047E-2</v>
+      </c>
+      <c r="H3">
+        <f>_xlfn.STDEV.S(C2:C19)</f>
+        <v>3.9821018649034137E-3</v>
+      </c>
+      <c r="J3" s="1"/>
+    </row>
+    <row r="4" spans="1:11" ht="42.75">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1">
+        <v>18.452491695077299</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.297161130585052</v>
+      </c>
+      <c r="G4">
+        <f>G3/G2/SQRT(COUNT(B2:B19))</f>
+        <v>1.1643295577687099E-3</v>
+      </c>
+      <c r="H4">
+        <f>H3/H2/SQRT(COUNT(C2:C19))</f>
+        <v>3.1059913870542803E-3</v>
+      </c>
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" spans="1:11" ht="42.75">
+      <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="1">
-        <v>0.39090251610402299</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="1">
-        <v>18.346083770183299</v>
-      </c>
-      <c r="G3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H3">
-        <f>_xlfn.STDEV.S(B2:B19)</f>
-        <v>5.1233545996458426E-3</v>
-      </c>
-      <c r="I3">
-        <f>_xlfn.STDEV.S(D2:D19)</f>
-        <v>9.0932068938100047E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="42.75">
-      <c r="A4" s="1" t="s">
+      <c r="B5" s="1">
+        <v>18.351915434355199</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.30092447877826201</v>
+      </c>
+      <c r="K5" s="1"/>
+    </row>
+    <row r="6" spans="1:11" ht="42.75">
+      <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="1">
-        <v>0.38163793874347302</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="1">
-        <v>18.452491695077299</v>
-      </c>
-      <c r="H4">
-        <f>H3/H2/SQRT(COUNT(B2:B19))</f>
-        <v>3.1111564954806109E-3</v>
-      </c>
-      <c r="I4">
-        <f>I3/I2/SQRT(COUNT(D2:D19))</f>
-        <v>1.1643295577687099E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="42.75">
-      <c r="A5" s="1" t="s">
+      <c r="B6" s="1">
+        <v>18.337397032620899</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.30225556251139701</v>
+      </c>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:11" ht="42.75">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1">
-        <v>0.38646897393750201</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="1">
-        <v>18.351915434355199</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="42.75">
-      <c r="A6" s="1" t="s">
+      <c r="B7" s="1">
+        <v>18.232394257417202</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.30453505035585898</v>
+      </c>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:11" ht="42.75">
+      <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="1">
-        <v>0.38820632020412599</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="1">
-        <v>18.337397032620899</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="42.75">
-      <c r="A7" s="1" t="s">
+      <c r="B8" s="1">
+        <v>18.415074041865601</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.29441937543381203</v>
+      </c>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:11" ht="42.75">
+      <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="1">
-        <v>0.391100077546855</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="1">
-        <v>18.232394257417202</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="42.75">
-      <c r="A8" s="1" t="s">
+      <c r="B9" s="1">
+        <v>18.341941017083698</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.29938049893952201</v>
+      </c>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:11" ht="42.75">
+      <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="1">
-        <v>0.37812534333091802</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="1">
-        <v>18.415074041865601</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="42.75">
-      <c r="A9" s="1" t="s">
+      <c r="B10" s="1">
+        <v>18.237027996635099</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.30198767465833298</v>
+      </c>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="1:11" ht="42.75">
+      <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="1">
-        <v>0.38449528426413199</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="1">
-        <v>18.341941017083698</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="42.75">
-      <c r="A10" s="1" t="s">
+      <c r="B11" s="1">
+        <v>18.531243546545401</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.29452133244947898</v>
+      </c>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:11" ht="42.75">
+      <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="1">
-        <v>0.38779470041263903</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="1">
-        <v>18.237027996635099</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="42.75">
-      <c r="A11" s="1" t="s">
+      <c r="B12" s="1">
+        <v>18.412716855394802</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0.30226636207287</v>
+      </c>
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:11" ht="42.75">
+      <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="1">
-        <v>0.378248054436716</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="1">
-        <v>18.531243546545401</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="42.75">
-      <c r="A12" s="1" t="s">
+      <c r="B13" s="1">
+        <v>18.4923898758226</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0.30276185184620003</v>
+      </c>
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:11" ht="42.75">
+      <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="1">
-        <v>0.388322173460803</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="1">
-        <v>18.412716855394802</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="42.75">
-      <c r="A13" s="1" t="s">
+      <c r="B14" s="1">
+        <v>18.515382021503999</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0.30565983998385898</v>
+      </c>
+      <c r="K14" s="1"/>
+    </row>
+    <row r="15" spans="1:11" ht="42.75">
+      <c r="A15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="1">
+        <v>18.391192672959299</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0.30235700258888798</v>
+      </c>
+      <c r="K15" s="1"/>
+    </row>
+    <row r="16" spans="1:11" ht="42.75">
+      <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="1">
-        <v>0.38881861759339797</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="1">
-        <v>18.4923898758226</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="42.75">
-      <c r="A14" s="1" t="s">
+      <c r="B16" s="1">
+        <v>18.551612310419799</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0.30470031507930101</v>
+      </c>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" spans="1:11" ht="42.75">
+      <c r="A17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="1">
+        <v>18.393990200449998</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0.30681032275950298</v>
+      </c>
+      <c r="K17" s="1"/>
+    </row>
+    <row r="18" spans="1:11" ht="42.75">
+      <c r="A18" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="1">
-        <v>0.39254780032303299</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="1">
-        <v>18.515382021503999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="42.75">
-      <c r="A15" s="1" t="s">
+      <c r="B18" s="1">
+        <v>18.450034969079201</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0.31003085423784599</v>
+      </c>
+      <c r="K18" s="1"/>
+    </row>
+    <row r="19" spans="1:11" ht="42.75">
+      <c r="A19" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="1">
-        <v>0.38860291038577099</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="1">
-        <v>18.391192672959299</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="42.75">
-      <c r="A16" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="1">
-        <v>0.391344107724999</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="1">
-        <v>18.551612310419799</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="42.75">
-      <c r="A17" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" s="1">
-        <v>0.39401793952400199</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" s="1">
-        <v>18.393990200449998</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="42.75">
-      <c r="A18" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" s="1">
-        <v>0.398157579716993</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="1">
-        <v>18.450034969079201</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="42.75">
-      <c r="A19" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="B19" s="1">
-        <v>0.38710256673105198</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" s="1">
         <v>18.408277105199002</v>
       </c>
+      <c r="C19" s="1">
+        <v>0.30130891367381502</v>
+      </c>
+      <c r="K19" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
